--- a/data/trans_orig/P6906-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6906-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43513</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>51665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>88289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>36394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73138</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>60934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81075</t>
+          <t>80287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>75313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95686</t>
+          <t>94592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>53597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>41458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146306</t>
+          <t>147232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171138</t>
+          <t>170881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183368</t>
+          <t>182435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209152</t>
+          <t>209317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>60375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47701</t>
+          <t>46944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59789</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100286</t>
+          <t>100878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117264</t>
+          <t>117489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154330</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>352</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365619</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>382619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172477</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>521</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538097</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>514362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>560019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>106686</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>88075</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>126925</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>47644</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>36699</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>60513</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>154330</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>133854</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>177728</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>365619</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>345380</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>384230</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>77,41%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>172477</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>159608</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>183422</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>78,36%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>538097</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>514699</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>558573</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>74,33%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3099,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45400</t>
+          <t>43590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3114,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35251</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,7 +3207,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>55738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3222,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31198</t>
+          <t>30952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53343</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>52993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>67637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75659</t>
+          <t>75633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94053</t>
+          <t>93853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34020</t>
+          <t>34124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>59126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>79819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98373</t>
+          <t>98147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>37594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53684</t>
+          <t>53585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123883</t>
+          <t>123915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149021</t>
+          <t>148917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>35096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35182</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49563</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66837</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84720</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148212</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241505</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257043</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151343</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392848</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326225</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541060</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541060</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541060</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>84720</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>68102</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>101429</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25,97%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>63492</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>50884</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>77900</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>148212</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>127966</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>169978</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>241505</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>224796</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>258123</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>74,03%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68,91%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>79,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>151343</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>136935</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>163951</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>392848</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>371082</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>413094</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>72,61%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>68,58%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>76,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>326225</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>326225</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>326225</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>214835</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>541060</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>541060</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>541060</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50448</t>
+          <t>50067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,93%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>42778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>62806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25657</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59416</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66690</t>
+          <t>66964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42953</t>
+          <t>43477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38320</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74777</t>
+          <t>75384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93916</t>
+          <t>93392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114092</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>45851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62891</t>
+          <t>63557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146169</t>
+          <t>145562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>173212</t>
+          <t>171720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55548</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66455</t>
+          <t>66405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40440</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88716</t>
+          <t>87522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>104219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83635</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70601</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154237</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266366</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145697</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412062</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>433556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>83635</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>101921</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>70601</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>57639</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>85697</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>39,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>154237</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>134773</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>177346</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>31,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>266366</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>248080</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>282636</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>80,75%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145697</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>130601</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>158659</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>60,38%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>412062</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>388953</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>431526</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>72,76%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>68,68%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>76,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28257</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80036</t>
+          <t>79836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33532</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45872</t>
+          <t>45996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>60631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77240</t>
+          <t>76874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53092</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66937</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>41531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43879</t>
+          <t>42699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>70410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>91687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114668</t>
+          <t>114008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71259</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85634</t>
+          <t>86314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168822</t>
+          <t>168566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195097</t>
+          <t>196277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +8998,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>35515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>42761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>50630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,7 +9106,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94883</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>118004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>142901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165443</t>
+          <t>166428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88673</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153115</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>277</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275063</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263619</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538682</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>515528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>64442</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>50125</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>82915</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>88673</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>63630</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>105808</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>153115</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>125543</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>177173</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>275063</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>256590</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>289380</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>81,02%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>85,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>263619</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>246484</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>288662</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>74,83%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>69,97%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>81,94%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>538682</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>514624</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>566254</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
